--- a/data_input/monthly/2026-09.xlsx
+++ b/data_input/monthly/2026-09.xlsx
@@ -8,21 +8,22 @@
   </bookViews>
   <sheets>
     <sheet name="_HƯỚNG DẪN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="booking" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="channel" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="daypart" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="identify" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="nature" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="fact_promo_day" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="recon" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="fact_lto_line" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="store_month" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="daily" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="coverage" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="member" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="voucher_month" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="voucher_join" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="cogs_cov" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="channel" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daypart" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="identify" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="nature" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="fact_promo_day" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="recon" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="fact_lto_line" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="fact_partner" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="booking" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="store_month" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="daily" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="coverage" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="member" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="voucher_month" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="voucher_join" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="cogs_cov" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +49,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00F3F2EE"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +71,11 @@
         <fgColor rgb="FFF2EFE6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F1F26"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -79,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -91,6 +101,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -636,250 +647,264 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   booking                    1 dòng   bắt buộc: month, status</t>
+          <t xml:space="preserve">   channel                    4 dòng   bắt buộc: month, channel</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
+          <t xml:space="preserve">                                  Doanh thu theo kênh bán (tại chỗ, mang về, giao hàng…).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   channel                    4 dòng   bắt buộc: month, channel</t>
+          <t xml:space="preserve">   daypart                    5 dòng   bắt buộc: month, daypart</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo kênh bán (tại chỗ, mang về, giao hàng…).</t>
+          <t xml:space="preserve">                                  Doanh thu theo khung giờ trong ngày.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daypart                    5 dòng   bắt buộc: month, daypart</t>
+          <t xml:space="preserve">   identify                   1 dòng   bắt buộc: month, bills, id_bills</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo khung giờ trong ngày.</t>
+          <t xml:space="preserve">                                  Tỷ lệ hoá đơn nhận diện được khách — trần trên của mọi phép quy doanh thu về khách. `items` = số dòng món đã xử lý trong tháng, nuôi thẻ đếm ở tab D1.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   identify                   1 dòng   bắt buộc: month, bills, id_bills</t>
+          <t xml:space="preserve">                                  loader tự tính: rate</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Tỷ lệ hoá đơn nhận diện được khách — trần trên của mọi phép quy doanh thu về khách. `items` = số dòng món đã xử lý trong tháng, nuôi thẻ đếm ở tab D1.</t>
+          <t xml:space="preserve">   nature                    14 dòng   bắt buộc: month, nature, brand, rev</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: rate</t>
+          <t xml:space="preserve">                                  Bản chất chương trình khuyến mãi. nature ∈ COMMERCIAL|INTERNAL|PARTNER|LOYALTY. `rev` = doanh thu chạm (cấp dòng món, THÀNH TIỀN) · `disc` = chiết khấu thật (cấp HOÁ ĐƠN) — hai base khác nhau, xem fact_promo_day.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   nature                    14 dòng   bắt buộc: month, nature, brand, rev</t>
+          <t xml:space="preserve">   fact_promo_day           410 dòng   bắt buộc: date, store, name_pos</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Bản chất chương trình khuyến mãi. nature ∈ COMMERCIAL|INTERNAL|PARTNER|LOYALTY. `rev` = doanh thu chạm (cấp dòng món, THÀNH TIỀN) · `disc` = chiết khấu thật (cấp HOÁ ĐƠN) — hai base khác nhau, xem fact_promo_day.</t>
+          <t xml:space="preserve">                                  CTKM theo NGÀY × cửa hàng — nền của M7.2. `disc` = Giảm giá + Chiết khấu ở cấp HOÁ ĐƠN · `voucher` = Phiếu GG, để riêng vì voucher là phương thức thanh toán chứ không phải giảm giá. `net` = Tổng tiền (cùng base với daily/store_month — kỳ nền của M7.2 lấy từ đó). `rev`/`items` từ lane dòng món theo THÀNH TIỀN — base khác `net`, đừng cộng chung. `name_pos` giữ nguyên văn, chuẩn hoá ở dim_campaign.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   fact_promo_day           410 dòng   bắt buộc: date, store, name_pos</t>
+          <t xml:space="preserve">   recon                     10 dòng   bắt buộc: month, store, net</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  CTKM theo NGÀY × cửa hàng — nền của M7.2. `disc` = Giảm giá + Chiết khấu ở cấp HOÁ ĐƠN · `voucher` = Phiếu GG, để riêng vì voucher là phương thức thanh toán chứ không phải giảm giá. `net` = Tổng tiền (cùng base với daily/store_month — kỳ nền của M7.2 lấy từ đó). `rev`/`items` từ lane dòng món theo THÀNH TIỀN — base khác `net`, đừng cộng chung. `name_pos` giữ nguyên văn, chuẩn hoá ở dim_campaign.</t>
+          <t xml:space="preserve">                                  Đối soát ba tầng: bảng tháng ↔ bảng món ↔ bảng hoá đơn.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   recon                     10 dòng   bắt buộc: month, store, net</t>
+          <t xml:space="preserve">                                  loader tự tính: d_bill</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Đối soát ba tầng: bảng tháng ↔ bảng món ↔ bảng hoá đơn.</t>
+          <t xml:space="preserve">   fact_lto_line              3 dòng   bắt buộc: date, store, bill, item_code</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: d_bill</t>
+          <t xml:space="preserve">                                  Dòng món thuộc nhóm LTO (Nhóm món chứa $campaign.lto_group_rx) gắn TỔNG hoá đơn chứa nó — nền doanh thu CTKM của chương trình LTO chạy theo món. `bill_net` = Tổng tiền cả hoá đơn (gồm món khác) · `line_rev` = Thành tiền riêng dòng LTO. Một hoá đơn có nhiều dòng LTO → cộng bill_net theo hoá đơn DUY NHẤT.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   fact_lto_line              3 dòng   bắt buộc: date, store, bill, item_code</t>
+          <t xml:space="preserve">   fact_partner              12 dòng   bắt buộc: store, partner, basis</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Dòng món thuộc nhóm LTO (Nhóm món chứa $campaign.lto_group_rx) gắn TỔNG hoá đơn chứa nó — nền doanh thu CTKM của chương trình LTO chạy theo món. `bill_net` = Tổng tiền cả hoá đơn (gồm món khác) · `line_rev` = Thành tiền riêng dòng LTO. Một hoá đơn có nhiều dòng LTO → cộng bill_net theo hoá đơn DUY NHẤT.</t>
+          <t xml:space="preserve">                                  Hoá đơn ĐỐI TÁC theo tháng × cửa hàng × đối tác — nền chung của M7 (thẻ Đối tác) và M9. Mỗi hoá đơn thuộc MỘT đối tác, nhận theo thứ tự `basis`: CTKM (tên CTKM khớp luật PARTNER, mã ở $promo_nature.rules[].partner) → NGUON (cột Nguồn là nền tảng) → PTTT (trả qua ví nền tảng). `camp` = tên CTKM nguyên văn (có thể rỗng). `net` = Tổng tiền (cùng base store_month) · `gross` = trước giảm giá · `disc` = Giảm giá + Chiết khấu · `voucher` = Phiếu GG · `commission` = cột Hoa hồng của POS.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   store_month               10 dòng   bắt buộc: month, store, net, guest, tc</t>
+          <t xml:space="preserve">   booking                    1 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
+          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
+          <t xml:space="preserve">   store_month               10 dòng   bắt buộc: month, store, net, guest, tc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daily                    109 dòng   bắt buộc: date, store, net</t>
+          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
+          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   daily                    109 dòng   bắt buộc: date, store, net</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
+          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: partial</t>
+          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   member                     1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Member đăng ký mới &amp; OA follow mới theo tháng (số toàn chuỗi).</t>
+          <t xml:space="preserve">                                  loader tự tính: partial</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_month              3 dòng   bắt buộc: m, brand</t>
+          <t xml:space="preserve">   member                     1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
+          <t xml:space="preserve">                                  Member đăng ký mới &amp; OA follow mới theo tháng (số toàn chuỗi).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_join               1 dòng   bắt buộc: m</t>
+          <t xml:space="preserve">   voucher_month              3 dòng   bắt buộc: m, brand</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Tỷ lệ voucher khớp được với hoá đơn trong cùng tháng.</t>
+          <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: rate</t>
+          <t xml:space="preserve">   voucher_join               1 dòng   bắt buộc: m</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   cogs_cov                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">                                  Tỷ lệ voucher khớp được với hoá đơn trong cùng tháng.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Độ phủ giá vốn theo tháng.</t>
+          <t xml:space="preserve">                                  loader tự tính: rate</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   cogs_cov                   1 dòng   bắt buộc: month</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  Độ phủ giá vốn theo tháng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">                                  loader tự tính: pct</t>
         </is>
@@ -891,3032 +916,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>net</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>gross</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>disc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1842000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>19</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1842000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2518050</v>
-      </c>
-      <c r="D3" t="n">
-        <v>32</v>
-      </c>
-      <c r="E3" t="n">
-        <v>28</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3466000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>947950</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>191393357</v>
-      </c>
-      <c r="D4" t="n">
-        <v>983</v>
-      </c>
-      <c r="E4" t="n">
-        <v>552</v>
-      </c>
-      <c r="F4" t="n">
-        <v>209351857</v>
-      </c>
-      <c r="G4" t="n">
-        <v>17958500</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>245828659</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1392</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1016</v>
-      </c>
-      <c r="F5" t="n">
-        <v>252819859</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6991200</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>418500</v>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>591000</v>
-      </c>
-      <c r="G6" t="n">
-        <v>172500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>508592286</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2837</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1604</v>
-      </c>
-      <c r="F7" t="n">
-        <v>537114186</v>
-      </c>
-      <c r="G7" t="n">
-        <v>28521900</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>492155541</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1620</v>
-      </c>
-      <c r="E8" t="n">
-        <v>762</v>
-      </c>
-      <c r="F8" t="n">
-        <v>521534241</v>
-      </c>
-      <c r="G8" t="n">
-        <v>29378700</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>415651100</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1465</v>
-      </c>
-      <c r="E9" t="n">
-        <v>671</v>
-      </c>
-      <c r="F9" t="n">
-        <v>443642200</v>
-      </c>
-      <c r="G9" t="n">
-        <v>27991100</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>382754580</v>
-      </c>
-      <c r="D10" t="n">
-        <v>556</v>
-      </c>
-      <c r="E10" t="n">
-        <v>223</v>
-      </c>
-      <c r="F10" t="n">
-        <v>411043930</v>
-      </c>
-      <c r="G10" t="n">
-        <v>28289350</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>135479927</v>
-      </c>
-      <c r="D11" t="n">
-        <v>213</v>
-      </c>
-      <c r="E11" t="n">
-        <v>88</v>
-      </c>
-      <c r="F11" t="n">
-        <v>147142827</v>
-      </c>
-      <c r="G11" t="n">
-        <v>11662900</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E110"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>net</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>guest</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>57164650</v>
-      </c>
-      <c r="D2" t="n">
-        <v>362</v>
-      </c>
-      <c r="E2" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>65500055</v>
-      </c>
-      <c r="D3" t="n">
-        <v>205</v>
-      </c>
-      <c r="E3" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>36299597</v>
-      </c>
-      <c r="D4" t="n">
-        <v>178</v>
-      </c>
-      <c r="E4" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>39011767</v>
-      </c>
-      <c r="D5" t="n">
-        <v>43</v>
-      </c>
-      <c r="E5" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>8817127</v>
-      </c>
-      <c r="D6" t="n">
-        <v>14</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>76029900</v>
-      </c>
-      <c r="D7" t="n">
-        <v>433</v>
-      </c>
-      <c r="E7" t="n">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>59520675</v>
-      </c>
-      <c r="D8" t="n">
-        <v>210</v>
-      </c>
-      <c r="E8" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>50327813</v>
-      </c>
-      <c r="D9" t="n">
-        <v>202</v>
-      </c>
-      <c r="E9" t="n">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>50473891</v>
-      </c>
-      <c r="D10" t="n">
-        <v>85</v>
-      </c>
-      <c r="E10" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>12849435</v>
-      </c>
-      <c r="D11" t="n">
-        <v>19</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>282000</v>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>16124650</v>
-      </c>
-      <c r="D13" t="n">
-        <v>79</v>
-      </c>
-      <c r="E13" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>15559550</v>
-      </c>
-      <c r="D14" t="n">
-        <v>108</v>
-      </c>
-      <c r="E14" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>47200</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>26929500</v>
-      </c>
-      <c r="D16" t="n">
-        <v>200</v>
-      </c>
-      <c r="E16" t="n">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>23888535</v>
-      </c>
-      <c r="D17" t="n">
-        <v>83</v>
-      </c>
-      <c r="E17" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>26334540</v>
-      </c>
-      <c r="D18" t="n">
-        <v>97</v>
-      </c>
-      <c r="E18" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>25165072</v>
-      </c>
-      <c r="D19" t="n">
-        <v>29</v>
-      </c>
-      <c r="E19" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>20543665</v>
-      </c>
-      <c r="D20" t="n">
-        <v>38</v>
-      </c>
-      <c r="E20" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>293000</v>
-      </c>
-      <c r="D21" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>9930050</v>
-      </c>
-      <c r="D22" t="n">
-        <v>97</v>
-      </c>
-      <c r="E22" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>19827350</v>
-      </c>
-      <c r="D23" t="n">
-        <v>120</v>
-      </c>
-      <c r="E23" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>47200</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>24797850</v>
-      </c>
-      <c r="D25" t="n">
-        <v>138</v>
-      </c>
-      <c r="E25" t="n">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>31124448</v>
-      </c>
-      <c r="D26" t="n">
-        <v>99</v>
-      </c>
-      <c r="E26" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>22319163</v>
-      </c>
-      <c r="D27" t="n">
-        <v>74</v>
-      </c>
-      <c r="E27" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>19306390</v>
-      </c>
-      <c r="D28" t="n">
-        <v>25</v>
-      </c>
-      <c r="E28" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>6733486</v>
-      </c>
-      <c r="D29" t="n">
-        <v>8</v>
-      </c>
-      <c r="E29" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>120750</v>
-      </c>
-      <c r="D30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>12403836</v>
-      </c>
-      <c r="D31" t="n">
-        <v>73</v>
-      </c>
-      <c r="E31" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>15957032</v>
-      </c>
-      <c r="D32" t="n">
-        <v>76</v>
-      </c>
-      <c r="E32" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>36858336</v>
-      </c>
-      <c r="D33" t="n">
-        <v>219</v>
-      </c>
-      <c r="E33" t="n">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>42547460</v>
-      </c>
-      <c r="D34" t="n">
-        <v>123</v>
-      </c>
-      <c r="E34" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>36397116</v>
-      </c>
-      <c r="D35" t="n">
-        <v>106</v>
-      </c>
-      <c r="E35" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>20607854</v>
-      </c>
-      <c r="D36" t="n">
-        <v>27</v>
-      </c>
-      <c r="E36" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>6114528</v>
-      </c>
-      <c r="D37" t="n">
-        <v>8</v>
-      </c>
-      <c r="E37" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>49000</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>18061667</v>
-      </c>
-      <c r="D39" t="n">
-        <v>77</v>
-      </c>
-      <c r="E39" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>20437843</v>
-      </c>
-      <c r="D40" t="n">
-        <v>103</v>
-      </c>
-      <c r="E40" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>41991177</v>
-      </c>
-      <c r="D41" t="n">
-        <v>200</v>
-      </c>
-      <c r="E41" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>40839871</v>
-      </c>
-      <c r="D42" t="n">
-        <v>127</v>
-      </c>
-      <c r="E42" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>26760762</v>
-      </c>
-      <c r="D43" t="n">
-        <v>92</v>
-      </c>
-      <c r="E43" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>17121661</v>
-      </c>
-      <c r="D44" t="n">
-        <v>27</v>
-      </c>
-      <c r="E44" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>7628418</v>
-      </c>
-      <c r="D45" t="n">
-        <v>14</v>
-      </c>
-      <c r="E45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>118000</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>198900</v>
-      </c>
-      <c r="D47" t="n">
-        <v>3</v>
-      </c>
-      <c r="E47" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>23708429</v>
-      </c>
-      <c r="D48" t="n">
-        <v>83</v>
-      </c>
-      <c r="E48" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>20660866</v>
-      </c>
-      <c r="D49" t="n">
-        <v>158</v>
-      </c>
-      <c r="E49" t="n">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>103500</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>31830188</v>
-      </c>
-      <c r="D51" t="n">
-        <v>192</v>
-      </c>
-      <c r="E51" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>18828033</v>
-      </c>
-      <c r="D52" t="n">
-        <v>72</v>
-      </c>
-      <c r="E52" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>17584905</v>
-      </c>
-      <c r="D53" t="n">
-        <v>61</v>
-      </c>
-      <c r="E53" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>16970805</v>
-      </c>
-      <c r="D54" t="n">
-        <v>32</v>
-      </c>
-      <c r="E54" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>7010672</v>
-      </c>
-      <c r="D55" t="n">
-        <v>11</v>
-      </c>
-      <c r="E55" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>128000</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>512000</v>
-      </c>
-      <c r="D57" t="n">
-        <v>6</v>
-      </c>
-      <c r="E57" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>19419028</v>
-      </c>
-      <c r="D58" t="n">
-        <v>124</v>
-      </c>
-      <c r="E58" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>29016670</v>
-      </c>
-      <c r="D59" t="n">
-        <v>168</v>
-      </c>
-      <c r="E59" t="n">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>79000</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>33977831</v>
-      </c>
-      <c r="D61" t="n">
-        <v>190</v>
-      </c>
-      <c r="E61" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>24110028</v>
-      </c>
-      <c r="D62" t="n">
-        <v>90</v>
-      </c>
-      <c r="E62" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>27996699</v>
-      </c>
-      <c r="D63" t="n">
-        <v>103</v>
-      </c>
-      <c r="E63" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>26741194</v>
-      </c>
-      <c r="D64" t="n">
-        <v>45</v>
-      </c>
-      <c r="E64" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>6175088</v>
-      </c>
-      <c r="D65" t="n">
-        <v>10</v>
-      </c>
-      <c r="E65" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>430000</v>
-      </c>
-      <c r="D66" t="n">
-        <v>6</v>
-      </c>
-      <c r="E66" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>15763088</v>
-      </c>
-      <c r="D67" t="n">
-        <v>87</v>
-      </c>
-      <c r="E67" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>19120069</v>
-      </c>
-      <c r="D68" t="n">
-        <v>123</v>
-      </c>
-      <c r="E68" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>47200</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>26225767</v>
-      </c>
-      <c r="D70" t="n">
-        <v>148</v>
-      </c>
-      <c r="E70" t="n">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>18656610</v>
-      </c>
-      <c r="D71" t="n">
-        <v>76</v>
-      </c>
-      <c r="E71" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>37891821</v>
-      </c>
-      <c r="D72" t="n">
-        <v>115</v>
-      </c>
-      <c r="E72" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>47681814</v>
-      </c>
-      <c r="D73" t="n">
-        <v>68</v>
-      </c>
-      <c r="E73" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>9709006</v>
-      </c>
-      <c r="D74" t="n">
-        <v>25</v>
-      </c>
-      <c r="E74" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>647000</v>
-      </c>
-      <c r="D75" t="n">
-        <v>4</v>
-      </c>
-      <c r="E75" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>524850</v>
-      </c>
-      <c r="D76" t="n">
-        <v>6</v>
-      </c>
-      <c r="E76" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>22980258</v>
-      </c>
-      <c r="D77" t="n">
-        <v>126</v>
-      </c>
-      <c r="E77" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>36714768</v>
-      </c>
-      <c r="D78" t="n">
-        <v>191</v>
-      </c>
-      <c r="E78" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>47200</v>
-      </c>
-      <c r="D79" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>30649017</v>
-      </c>
-      <c r="D80" t="n">
-        <v>124</v>
-      </c>
-      <c r="E80" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>46569781</v>
-      </c>
-      <c r="D81" t="n">
-        <v>115</v>
-      </c>
-      <c r="E81" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>49974928</v>
-      </c>
-      <c r="D82" t="n">
-        <v>143</v>
-      </c>
-      <c r="E82" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>42790101</v>
-      </c>
-      <c r="D83" t="n">
-        <v>65</v>
-      </c>
-      <c r="E83" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>10627470</v>
-      </c>
-      <c r="D84" t="n">
-        <v>15</v>
-      </c>
-      <c r="E84" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>IFC_SIG</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>237000</v>
-      </c>
-      <c r="D85" t="n">
-        <v>2</v>
-      </c>
-      <c r="E85" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>311950</v>
-      </c>
-      <c r="D86" t="n">
-        <v>3</v>
-      </c>
-      <c r="E86" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>19606150</v>
-      </c>
-      <c r="D87" t="n">
-        <v>99</v>
-      </c>
-      <c r="E87" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>24773990</v>
-      </c>
-      <c r="D88" t="n">
-        <v>127</v>
-      </c>
-      <c r="E88" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>NCB_NDC</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>47200</v>
-      </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>27093952</v>
-      </c>
-      <c r="D90" t="n">
-        <v>148</v>
-      </c>
-      <c r="E90" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>32568821</v>
-      </c>
-      <c r="D91" t="n">
-        <v>92</v>
-      </c>
-      <c r="E91" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>21750433</v>
-      </c>
-      <c r="D92" t="n">
-        <v>77</v>
-      </c>
-      <c r="E92" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>11490230</v>
-      </c>
-      <c r="D93" t="n">
-        <v>20</v>
-      </c>
-      <c r="E93" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>14348956</v>
-      </c>
-      <c r="D94" t="n">
-        <v>18</v>
-      </c>
-      <c r="E94" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>274500</v>
-      </c>
-      <c r="D95" t="n">
-        <v>3</v>
-      </c>
-      <c r="E95" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>23021575</v>
-      </c>
-      <c r="D96" t="n">
-        <v>90</v>
-      </c>
-      <c r="E96" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>14678224</v>
-      </c>
-      <c r="D97" t="n">
-        <v>76</v>
-      </c>
-      <c r="E97" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>39820751</v>
-      </c>
-      <c r="D98" t="n">
-        <v>218</v>
-      </c>
-      <c r="E98" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>39056495</v>
-      </c>
-      <c r="D99" t="n">
-        <v>139</v>
-      </c>
-      <c r="E99" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>32078382</v>
-      </c>
-      <c r="D100" t="n">
-        <v>106</v>
-      </c>
-      <c r="E100" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>27582618</v>
-      </c>
-      <c r="D101" t="n">
-        <v>43</v>
-      </c>
-      <c r="E101" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>15307853</v>
-      </c>
-      <c r="D102" t="n">
-        <v>19</v>
-      </c>
-      <c r="E102" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>NCB_9ST</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>233100</v>
-      </c>
-      <c r="D103" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>NCB_ET</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>10374626</v>
-      </c>
-      <c r="D104" t="n">
-        <v>48</v>
-      </c>
-      <c r="E104" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>NCB_MET</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>29082297</v>
-      </c>
-      <c r="D105" t="n">
-        <v>142</v>
-      </c>
-      <c r="E105" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>NCB_SKC</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>55223367</v>
-      </c>
-      <c r="D106" t="n">
-        <v>265</v>
-      </c>
-      <c r="E106" t="n">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>NDC_BKL</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>48944729</v>
-      </c>
-      <c r="D107" t="n">
-        <v>189</v>
-      </c>
-      <c r="E107" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>NDC_NTMK</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>29934941</v>
-      </c>
-      <c r="D108" t="n">
-        <v>111</v>
-      </c>
-      <c r="E108" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>NJFB_CRE</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>37811183</v>
-      </c>
-      <c r="D109" t="n">
-        <v>47</v>
-      </c>
-      <c r="E109" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>NJFB_SSV</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>9614223</v>
-      </c>
-      <c r="D110" t="n">
-        <v>14</v>
-      </c>
-      <c r="E110" t="n">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>days_data</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>days_month</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>first</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>last</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>member</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>oa</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>days</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>brand</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>used</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>rev</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>disc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NCB</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>59</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16473000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2766900</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NDC</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D3" t="n">
-        <v>14017000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2753400</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NJFB</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>12076000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2343200</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>hit</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>83</v>
-      </c>
-      <c r="C2" t="n">
-        <v>83</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>rev</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>rev_cov</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>sku</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>sku_cov</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2275409082</v>
-      </c>
-      <c r="C2" t="n">
-        <v>219067000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>615</v>
-      </c>
-      <c r="E2" t="n">
-        <v>98</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0963</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4115,7 +1114,3013 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1842000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1842000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2518050</v>
+      </c>
+      <c r="D3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3466000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>947950</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>191393357</v>
+      </c>
+      <c r="D4" t="n">
+        <v>983</v>
+      </c>
+      <c r="E4" t="n">
+        <v>552</v>
+      </c>
+      <c r="F4" t="n">
+        <v>209351857</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17958500</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>245828659</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1392</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1016</v>
+      </c>
+      <c r="F5" t="n">
+        <v>252819859</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6991200</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>418500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>591000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>172500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>508592286</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2837</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1604</v>
+      </c>
+      <c r="F7" t="n">
+        <v>537114186</v>
+      </c>
+      <c r="G7" t="n">
+        <v>28521900</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>492155541</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1620</v>
+      </c>
+      <c r="E8" t="n">
+        <v>762</v>
+      </c>
+      <c r="F8" t="n">
+        <v>521534241</v>
+      </c>
+      <c r="G8" t="n">
+        <v>29378700</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>415651100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E9" t="n">
+        <v>671</v>
+      </c>
+      <c r="F9" t="n">
+        <v>443642200</v>
+      </c>
+      <c r="G9" t="n">
+        <v>27991100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>382754580</v>
+      </c>
+      <c r="D10" t="n">
+        <v>556</v>
+      </c>
+      <c r="E10" t="n">
+        <v>223</v>
+      </c>
+      <c r="F10" t="n">
+        <v>411043930</v>
+      </c>
+      <c r="G10" t="n">
+        <v>28289350</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>135479927</v>
+      </c>
+      <c r="D11" t="n">
+        <v>213</v>
+      </c>
+      <c r="E11" t="n">
+        <v>88</v>
+      </c>
+      <c r="F11" t="n">
+        <v>147142827</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11662900</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>57164650</v>
+      </c>
+      <c r="D2" t="n">
+        <v>362</v>
+      </c>
+      <c r="E2" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>65500055</v>
+      </c>
+      <c r="D3" t="n">
+        <v>205</v>
+      </c>
+      <c r="E3" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>36299597</v>
+      </c>
+      <c r="D4" t="n">
+        <v>178</v>
+      </c>
+      <c r="E4" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>39011767</v>
+      </c>
+      <c r="D5" t="n">
+        <v>43</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>8817127</v>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>76029900</v>
+      </c>
+      <c r="D7" t="n">
+        <v>433</v>
+      </c>
+      <c r="E7" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>59520675</v>
+      </c>
+      <c r="D8" t="n">
+        <v>210</v>
+      </c>
+      <c r="E8" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>50327813</v>
+      </c>
+      <c r="D9" t="n">
+        <v>202</v>
+      </c>
+      <c r="E9" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>50473891</v>
+      </c>
+      <c r="D10" t="n">
+        <v>85</v>
+      </c>
+      <c r="E10" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12849435</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>282000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>16124650</v>
+      </c>
+      <c r="D13" t="n">
+        <v>79</v>
+      </c>
+      <c r="E13" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>15559550</v>
+      </c>
+      <c r="D14" t="n">
+        <v>108</v>
+      </c>
+      <c r="E14" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>47200</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>26929500</v>
+      </c>
+      <c r="D16" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>23888535</v>
+      </c>
+      <c r="D17" t="n">
+        <v>83</v>
+      </c>
+      <c r="E17" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>26334540</v>
+      </c>
+      <c r="D18" t="n">
+        <v>97</v>
+      </c>
+      <c r="E18" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>25165072</v>
+      </c>
+      <c r="D19" t="n">
+        <v>29</v>
+      </c>
+      <c r="E19" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>20543665</v>
+      </c>
+      <c r="D20" t="n">
+        <v>38</v>
+      </c>
+      <c r="E20" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>293000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9930050</v>
+      </c>
+      <c r="D22" t="n">
+        <v>97</v>
+      </c>
+      <c r="E22" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>19827350</v>
+      </c>
+      <c r="D23" t="n">
+        <v>120</v>
+      </c>
+      <c r="E23" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>47200</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>24797850</v>
+      </c>
+      <c r="D25" t="n">
+        <v>138</v>
+      </c>
+      <c r="E25" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>31124448</v>
+      </c>
+      <c r="D26" t="n">
+        <v>99</v>
+      </c>
+      <c r="E26" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>22319163</v>
+      </c>
+      <c r="D27" t="n">
+        <v>74</v>
+      </c>
+      <c r="E27" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>19306390</v>
+      </c>
+      <c r="D28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6733486</v>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>120750</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>12403836</v>
+      </c>
+      <c r="D31" t="n">
+        <v>73</v>
+      </c>
+      <c r="E31" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>15957032</v>
+      </c>
+      <c r="D32" t="n">
+        <v>76</v>
+      </c>
+      <c r="E32" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>36858336</v>
+      </c>
+      <c r="D33" t="n">
+        <v>219</v>
+      </c>
+      <c r="E33" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>42547460</v>
+      </c>
+      <c r="D34" t="n">
+        <v>123</v>
+      </c>
+      <c r="E34" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>36397116</v>
+      </c>
+      <c r="D35" t="n">
+        <v>106</v>
+      </c>
+      <c r="E35" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>20607854</v>
+      </c>
+      <c r="D36" t="n">
+        <v>27</v>
+      </c>
+      <c r="E36" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>6114528</v>
+      </c>
+      <c r="D37" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>49000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>18061667</v>
+      </c>
+      <c r="D39" t="n">
+        <v>77</v>
+      </c>
+      <c r="E39" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>20437843</v>
+      </c>
+      <c r="D40" t="n">
+        <v>103</v>
+      </c>
+      <c r="E40" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>41991177</v>
+      </c>
+      <c r="D41" t="n">
+        <v>200</v>
+      </c>
+      <c r="E41" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>40839871</v>
+      </c>
+      <c r="D42" t="n">
+        <v>127</v>
+      </c>
+      <c r="E42" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>26760762</v>
+      </c>
+      <c r="D43" t="n">
+        <v>92</v>
+      </c>
+      <c r="E43" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>17121661</v>
+      </c>
+      <c r="D44" t="n">
+        <v>27</v>
+      </c>
+      <c r="E44" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>7628418</v>
+      </c>
+      <c r="D45" t="n">
+        <v>14</v>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>198900</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>23708429</v>
+      </c>
+      <c r="D48" t="n">
+        <v>83</v>
+      </c>
+      <c r="E48" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>20660866</v>
+      </c>
+      <c r="D49" t="n">
+        <v>158</v>
+      </c>
+      <c r="E49" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>103500</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>31830188</v>
+      </c>
+      <c r="D51" t="n">
+        <v>192</v>
+      </c>
+      <c r="E51" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>18828033</v>
+      </c>
+      <c r="D52" t="n">
+        <v>72</v>
+      </c>
+      <c r="E52" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>17584905</v>
+      </c>
+      <c r="D53" t="n">
+        <v>61</v>
+      </c>
+      <c r="E53" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16970805</v>
+      </c>
+      <c r="D54" t="n">
+        <v>32</v>
+      </c>
+      <c r="E54" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7010672</v>
+      </c>
+      <c r="D55" t="n">
+        <v>11</v>
+      </c>
+      <c r="E55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>128000</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>512000</v>
+      </c>
+      <c r="D57" t="n">
+        <v>6</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>19419028</v>
+      </c>
+      <c r="D58" t="n">
+        <v>124</v>
+      </c>
+      <c r="E58" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>29016670</v>
+      </c>
+      <c r="D59" t="n">
+        <v>168</v>
+      </c>
+      <c r="E59" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>79000</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>33977831</v>
+      </c>
+      <c r="D61" t="n">
+        <v>190</v>
+      </c>
+      <c r="E61" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>24110028</v>
+      </c>
+      <c r="D62" t="n">
+        <v>90</v>
+      </c>
+      <c r="E62" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>27996699</v>
+      </c>
+      <c r="D63" t="n">
+        <v>103</v>
+      </c>
+      <c r="E63" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>26741194</v>
+      </c>
+      <c r="D64" t="n">
+        <v>45</v>
+      </c>
+      <c r="E64" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>6175088</v>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>430000</v>
+      </c>
+      <c r="D66" t="n">
+        <v>6</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>15763088</v>
+      </c>
+      <c r="D67" t="n">
+        <v>87</v>
+      </c>
+      <c r="E67" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>19120069</v>
+      </c>
+      <c r="D68" t="n">
+        <v>123</v>
+      </c>
+      <c r="E68" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>47200</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>26225767</v>
+      </c>
+      <c r="D70" t="n">
+        <v>148</v>
+      </c>
+      <c r="E70" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>18656610</v>
+      </c>
+      <c r="D71" t="n">
+        <v>76</v>
+      </c>
+      <c r="E71" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>37891821</v>
+      </c>
+      <c r="D72" t="n">
+        <v>115</v>
+      </c>
+      <c r="E72" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>47681814</v>
+      </c>
+      <c r="D73" t="n">
+        <v>68</v>
+      </c>
+      <c r="E73" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>9709006</v>
+      </c>
+      <c r="D74" t="n">
+        <v>25</v>
+      </c>
+      <c r="E74" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>647000</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>524850</v>
+      </c>
+      <c r="D76" t="n">
+        <v>6</v>
+      </c>
+      <c r="E76" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>22980258</v>
+      </c>
+      <c r="D77" t="n">
+        <v>126</v>
+      </c>
+      <c r="E77" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>36714768</v>
+      </c>
+      <c r="D78" t="n">
+        <v>191</v>
+      </c>
+      <c r="E78" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>47200</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>30649017</v>
+      </c>
+      <c r="D80" t="n">
+        <v>124</v>
+      </c>
+      <c r="E80" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>46569781</v>
+      </c>
+      <c r="D81" t="n">
+        <v>115</v>
+      </c>
+      <c r="E81" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>49974928</v>
+      </c>
+      <c r="D82" t="n">
+        <v>143</v>
+      </c>
+      <c r="E82" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>42790101</v>
+      </c>
+      <c r="D83" t="n">
+        <v>65</v>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>10627470</v>
+      </c>
+      <c r="D84" t="n">
+        <v>15</v>
+      </c>
+      <c r="E84" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>IFC_SIG</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>237000</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>311950</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>19606150</v>
+      </c>
+      <c r="D87" t="n">
+        <v>99</v>
+      </c>
+      <c r="E87" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>24773990</v>
+      </c>
+      <c r="D88" t="n">
+        <v>127</v>
+      </c>
+      <c r="E88" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NCB_NDC</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>47200</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>27093952</v>
+      </c>
+      <c r="D90" t="n">
+        <v>148</v>
+      </c>
+      <c r="E90" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>32568821</v>
+      </c>
+      <c r="D91" t="n">
+        <v>92</v>
+      </c>
+      <c r="E91" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>21750433</v>
+      </c>
+      <c r="D92" t="n">
+        <v>77</v>
+      </c>
+      <c r="E92" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>11490230</v>
+      </c>
+      <c r="D93" t="n">
+        <v>20</v>
+      </c>
+      <c r="E93" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>14348956</v>
+      </c>
+      <c r="D94" t="n">
+        <v>18</v>
+      </c>
+      <c r="E94" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>274500</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>23021575</v>
+      </c>
+      <c r="D96" t="n">
+        <v>90</v>
+      </c>
+      <c r="E96" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>14678224</v>
+      </c>
+      <c r="D97" t="n">
+        <v>76</v>
+      </c>
+      <c r="E97" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>39820751</v>
+      </c>
+      <c r="D98" t="n">
+        <v>218</v>
+      </c>
+      <c r="E98" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>39056495</v>
+      </c>
+      <c r="D99" t="n">
+        <v>139</v>
+      </c>
+      <c r="E99" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>32078382</v>
+      </c>
+      <c r="D100" t="n">
+        <v>106</v>
+      </c>
+      <c r="E100" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>27582618</v>
+      </c>
+      <c r="D101" t="n">
+        <v>43</v>
+      </c>
+      <c r="E101" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>15307853</v>
+      </c>
+      <c r="D102" t="n">
+        <v>19</v>
+      </c>
+      <c r="E102" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NCB_9ST</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>233100</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>10374626</v>
+      </c>
+      <c r="D104" t="n">
+        <v>48</v>
+      </c>
+      <c r="E104" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>29082297</v>
+      </c>
+      <c r="D105" t="n">
+        <v>142</v>
+      </c>
+      <c r="E105" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>55223367</v>
+      </c>
+      <c r="D106" t="n">
+        <v>265</v>
+      </c>
+      <c r="E106" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>48944729</v>
+      </c>
+      <c r="D107" t="n">
+        <v>189</v>
+      </c>
+      <c r="E107" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>29934941</v>
+      </c>
+      <c r="D108" t="n">
+        <v>111</v>
+      </c>
+      <c r="E108" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>37811183</v>
+      </c>
+      <c r="D109" t="n">
+        <v>47</v>
+      </c>
+      <c r="E109" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>9614223</v>
+      </c>
+      <c r="D110" t="n">
+        <v>14</v>
+      </c>
+      <c r="E110" t="n">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>days_data</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>days_month</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>first</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>last</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>member</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>oa</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>59</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16473000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2766900</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14017000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2753400</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12076000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2343200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>hit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>83</v>
+      </c>
+      <c r="C2" t="n">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>rev</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>rev_cov</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>sku</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>sku_cov</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2275409082</v>
+      </c>
+      <c r="C2" t="n">
+        <v>219067000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>615</v>
+      </c>
+      <c r="E2" t="n">
+        <v>98</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0963</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4229,7 +4234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4382,7 +4387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4440,7 +4445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4558,13 +4563,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>72802000</v>
+        <v>231261000</v>
       </c>
       <c r="E4" t="n">
-        <v>39865390</v>
+        <v>60687659</v>
       </c>
       <c r="F4" t="n">
-        <v>169</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5">
@@ -4584,13 +4589,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>118569000</v>
+        <v>132514000</v>
       </c>
       <c r="E5" t="n">
-        <v>56248640</v>
+        <v>64012856</v>
       </c>
       <c r="F5" t="n">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6">
@@ -4610,13 +4615,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78035000</v>
+        <v>118586000</v>
       </c>
       <c r="E6" t="n">
-        <v>19374220</v>
+        <v>43173963</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -4792,13 +4797,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>159655000</v>
+        <v>1196000</v>
       </c>
       <c r="E13" t="n">
-        <v>21001669</v>
+        <v>179400</v>
       </c>
       <c r="F13" t="n">
-        <v>464</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -4818,13 +4823,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>21943000</v>
+        <v>7998000</v>
       </c>
       <c r="E14" t="n">
-        <v>9364216</v>
+        <v>1600000</v>
       </c>
       <c r="F14" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -4844,13 +4849,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>47528000</v>
+        <v>6977000</v>
       </c>
       <c r="E15" t="n">
-        <v>24999743</v>
+        <v>1200000</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4858,7 +4863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5242,7 +5247,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -5293,7 +5298,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -5701,7 +5706,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -5887,7 +5892,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -6142,7 +6147,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -6244,7 +6249,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -6481,7 +6486,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -6583,7 +6588,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -7159,7 +7164,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -7363,7 +7368,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -7633,7 +7638,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -7870,7 +7875,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -7921,7 +7926,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -7972,7 +7977,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -8191,7 +8196,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -8242,7 +8247,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -8785,7 +8790,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -8887,7 +8892,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -9040,7 +9045,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -9445,7 +9450,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -9496,7 +9501,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -9547,7 +9552,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -9784,7 +9789,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -10072,7 +10077,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -10291,7 +10296,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -10444,7 +10449,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -10681,7 +10686,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -10732,7 +10737,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -10969,7 +10974,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -11275,7 +11280,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -11425,7 +11430,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -11662,7 +11667,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -11764,7 +11769,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -11848,7 +11853,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -11899,7 +11904,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -12085,7 +12090,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -12136,7 +12141,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -12493,7 +12498,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -12967,7 +12972,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -13135,7 +13140,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -13387,7 +13392,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -13438,7 +13443,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -13726,7 +13731,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -13777,7 +13782,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -14890,7 +14895,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F212" t="n">
@@ -15262,7 +15267,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F220" t="n">
@@ -15517,7 +15522,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -16408,7 +16413,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -16459,7 +16464,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -16510,7 +16515,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -16813,7 +16818,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -16864,7 +16869,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -17320,7 +17325,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F266" t="n">
@@ -17488,7 +17493,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -17590,7 +17595,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F272" t="n">
@@ -17809,7 +17814,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -18061,7 +18066,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -18112,7 +18117,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -18163,7 +18168,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -18400,7 +18405,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -18451,7 +18456,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F291" t="n">
@@ -18859,7 +18864,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F299" t="n">
@@ -19333,7 +19338,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F309" t="n">
@@ -19435,7 +19440,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F311" t="n">
@@ -19705,7 +19710,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F317" t="n">
@@ -20059,7 +20064,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F325" t="n">
@@ -20161,7 +20166,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F327" t="n">
@@ -20347,7 +20352,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -20398,7 +20403,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -20704,7 +20709,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F338" t="n">
@@ -21109,7 +21114,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F347" t="n">
@@ -21481,7 +21486,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F355" t="n">
@@ -21532,7 +21537,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F356" t="n">
@@ -21769,7 +21774,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F361" t="n">
@@ -21820,7 +21825,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F362" t="n">
@@ -22126,7 +22131,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F368" t="n">
@@ -22819,7 +22824,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F383" t="n">
@@ -23038,7 +23043,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F388" t="n">
@@ -23089,7 +23094,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F389" t="n">
@@ -23344,7 +23349,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F394" t="n">
@@ -23395,7 +23400,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F395" t="n">
@@ -23752,7 +23757,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F402" t="n">
@@ -24157,7 +24162,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>PARTNER</t>
+          <t>COMMERCIAL</t>
         </is>
       </c>
       <c r="F411" t="n">
@@ -24190,7 +24195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24592,7 +24597,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -24903,4 +24908,706 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>camp</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>bills</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>guests</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>gross</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>disc</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>voucher</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>commission</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CTKM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Noire - Techcombank Reward × OneU</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1196000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>179400</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1152826</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CTKM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dining - Techcombank Reward × OneU</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5578000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5195913</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CTKM</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dining - Techcombank Reward × OneU</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2420000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>600000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2063880</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CTKM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>JFB - Techcombank Reward × OneU</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1861000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>400000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1656774</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CTKM</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>JFB - Techcombank Reward × OneU</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5116000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>800000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4901014</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NGUON</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>34</v>
+      </c>
+      <c r="H7" t="n">
+        <v>75</v>
+      </c>
+      <c r="I7" t="n">
+        <v>21720000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>24616200</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NGUON</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>TẶNG QUÀ SINH NHẬT (Bánh Millie Crepe)</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6920000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>500000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7281540</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NDC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PTTT</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4149000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4704966</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NGUON</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>14</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7331000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8314173</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PTTT</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="n">
+        <v>26</v>
+      </c>
+      <c r="I11" t="n">
+        <v>13437000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15246546</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NJFB</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>P03</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PTTT</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I12" t="n">
+        <v>14505000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>16449489</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NCB_MET</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NCB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NGUON</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>415000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>112050</v>
+      </c>
+      <c r="M13" t="n">
+        <v>336150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data_input/monthly/2026-09.xlsx
+++ b/data_input/monthly/2026-09.xlsx
@@ -16,14 +16,15 @@
     <sheet name="recon" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="fact_lto_line" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="fact_partner" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="booking" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="store_month" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="daily" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="coverage" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="member" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="voucher_month" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="voucher_join" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="cogs_cov" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="daily_party" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="booking" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="store_month" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="daily" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="coverage" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="member" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="voucher_month" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="voucher_join" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="cogs_cov" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A67"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -773,138 +774,152 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   booking                    1 dòng   bắt buộc: month, status</t>
+          <t xml:space="preserve">   daily_party               15 dòng   bắt buộc: date, store, net, tc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
+          <t xml:space="preserve">                                  Phần KHÁCH TIỆC của `daily`: chỉ các hoá đơn có Số khách ≥ $guest_segment.party_min_guests, gộp theo NGÀY × cửa hàng. ETL tự sinh từ bảng kê hoá đơn (S02). Khách lẻ = daily − daily_party.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   store_month               10 dòng   bắt buộc: month, store, net, guest, tc</t>
+          <t xml:space="preserve">   booking                    1 dòng   bắt buộc: month, status</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
+          <t xml:space="preserve">                                  Booking tiệc &amp; sự kiện — gộp theo tháng NHẬN LEAD (month) × tháng DIỄN RA (ev_month) × cửa hàng × phân khúc × loại × nguồn × trạng thái. month = Inquiry Date → Input Date → (thiếu cả hai) ngày sự kiện, khi đó inq_est đếm số lead bị ước. seg ∈ event|table, stage ∈ won|open|lost — luật ở $booking. exp chỉ cộng ô có số (exp_n lead); ô trống/TBA KHÔNG tính là 0. closed_n = số lead Confirmed đã nhập Closed Revenue.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
+          <t xml:space="preserve">   store_month               10 dòng   bắt buộc: month, store, net, guest, tc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   daily                    109 dòng   bắt buộc: date, store, net</t>
+          <t xml:space="preserve">                                  XƯƠNG SỐNG của hệ thống. net = doanh thu thuần · guest = số khách · tc = số hoá đơn.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
+          <t xml:space="preserve">                                  loader tự tính: ta, aov, brand, tier</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">   daily                    109 dòng   bắt buộc: date, store, net</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
+          <t xml:space="preserve">                                  Doanh thu theo NGÀY × cửa hàng. Ngày phải nằm trong tháng của file.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: partial</t>
+          <t xml:space="preserve">   coverage                   1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   member                     1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">                                  Số ngày THỰC CÓ dữ liệu — nhận diện tháng chưa trọn kỳ. Không khai thì loader suy từ daily.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Member đăng ký mới &amp; OA follow mới theo tháng (số toàn chuỗi).</t>
+          <t xml:space="preserve">                                  loader tự tính: partial</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_month              3 dòng   bắt buộc: m, brand</t>
+          <t xml:space="preserve">   member                     1 dòng   bắt buộc: month</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
+          <t xml:space="preserve">                                  Member đăng ký mới &amp; OA follow mới theo tháng (số toàn chuỗi).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   voucher_join               1 dòng   bắt buộc: m</t>
+          <t xml:space="preserve">   voucher_month              3 dòng   bắt buộc: m, brand</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Tỷ lệ voucher khớp được với hoá đơn trong cùng tháng.</t>
+          <t xml:space="preserve">                                  Voucher đã dùng theo tháng × brand.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  loader tự tính: rate</t>
+          <t xml:space="preserve">   voucher_join               1 dòng   bắt buộc: m</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   cogs_cov                   1 dòng   bắt buộc: month</t>
+          <t xml:space="preserve">                                  Tỷ lệ voucher khớp được với hoá đơn trong cùng tháng.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">                                  Độ phủ giá vốn theo tháng.</t>
+          <t xml:space="preserve">                                  loader tự tính: rate</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   cogs_cov                   1 dòng   bắt buộc: month</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                  Độ phủ giá vốn theo tháng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">                                  loader tự tính: pct</t>
         </is>
@@ -916,6 +931,369 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>net</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>895860</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1036350</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13995912</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>8493600</v>
+      </c>
+      <c r="D5" t="n">
+        <v>35</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>805140</v>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>10852380</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2118312</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NDC_BKL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1046115</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>858155</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NCB_ET</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1695330</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16651530</v>
+      </c>
+      <c r="D12" t="n">
+        <v>34</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NJFB_SSV</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2195550</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NDC_NTMK</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>18738304</v>
+      </c>
+      <c r="D14" t="n">
+        <v>38</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NJFB_CRE</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10587969</v>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NCB_SKC</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>652050</v>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1114,7 +1492,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1444,7 +1822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3781,7 +4159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3852,7 +4230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3904,7 +4282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4008,7 +4386,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4052,7 +4430,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25390,7 +25768,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PTTT</t>
+          <t>XAC_NHAN</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -25486,7 +25864,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PTTT</t>
+          <t>XAC_NHAN</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -25534,7 +25912,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PTTT</t>
+          <t>XAC_NHAN</t>
         </is>
       </c>
       <c r="G12" t="n">
